--- a/ingest/2026-09-03/canadian_standard_ls_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/canadian_standard_ls_upload_2026-09-03.xlsx
@@ -7375,7 +7375,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Reducer | Engineered | Cut Order (per linear ft)</t>
+          <t>Canadian Standard - Transition | Reducer | Wood | Cut Order (per linear ft)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Stair Nosing | Engineered | Cut Order (per linear ft)</t>
+          <t>Canadian Standard - Transition | Stair Nosing | Wood | Cut Order (per linear ft)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | T-Moulding | Engineered | Cut Order (per linear ft)</t>
+          <t>Canadian Standard - Transition | T-Moulding | Wood | Cut Order (per linear ft)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Reducer | Laminate | 8 ft.</t>
+          <t>Canadian Standard - Transition | Reducer | Laminate | 8 ft. (Inhaus Laminate)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Stair Nosing | Laminate | 8 ft.</t>
+          <t>Canadian Standard - Transition | Stair Nosing | Laminate | 8 ft. (Inhaus Laminate)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | T-Moulding | Laminate | 8 ft.</t>
+          <t>Canadian Standard - Transition | T-Moulding | Laminate | 8 ft. (Inhaus Laminate)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Reducer | LVP | 94"</t>
+          <t>Canadian Standard - Transition | Reducer | SPC | 94" (Eclipse)</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Stair Nosing | LVP | 94"</t>
+          <t>Canadian Standard - Transition | Stair Nosing | SPC | 94" (Eclipse)</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | T-Moulding | LVP | 94"</t>
+          <t>Canadian Standard - Transition | T-Moulding | SPC | 94" (Eclipse)</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">

--- a/ingest/2026-09-03/canadian_standard_ls_upload_2026-09-03.xlsx
+++ b/ingest/2026-09-03/canadian_standard_ls_upload_2026-09-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE340"/>
+  <dimension ref="A1:AE337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20840,7 +20840,7 @@
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>CANSVANNTETTPLUSREDUCER</t>
+          <t>CANSVANNTETTREDUCER</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Reducer | SPC | 2400mm x 45mm x 7mm (VANNTETT PLUS)</t>
+          <t>Canadian Standard - Transition | Reducer | SPC | 2400mm x 45mm x 7mm (VANNTETT PLUS / VANNTETTPRO)</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20898,7 +20898,7 @@
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>CANSVANNTETTPLUSSTAIRNOSING</t>
+          <t>CANSVANNTETTSTAIRNOSING</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | Stair Nosing | SPC | 2400mm x 53mm x 18mm (VANNTETT PLUS)</t>
+          <t>Canadian Standard - Transition | Stair Nosing | SPC | 2400mm x 53mm x 18mm (VANNTETT PLUS / VANNTETTPRO)</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>CANSVANNTETTPLUSTMOULDING</t>
+          <t>CANSVANNTETTTMOULDING</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Canadian Standard - Transition | T-Moulding | SPC | 2400mm x 45mm x 7mm (VANNTETT PLUS)</t>
+          <t>Canadian Standard - Transition | T-Moulding | SPC | 2400mm x 45mm x 7mm (VANNTETT PLUS / VANNTETTPRO)</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21510,180 +21510,6 @@
         </is>
       </c>
       <c r="AB337" t="inlineStr">
-        <is>
-          <t>Default Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>CANSVANNTETTPROREDUCER</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>ACC-CANS-0011</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>Canadian Standard - Transition | Reducer | SPC | 2400mm x 45mm x 7mm (VANNTETTPRO)</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>Sold per piece | Last price update: 2026-08-31 | Price last changed by: Manual | Active: TRUE | Salesperson notes: Per-piece trim, 2400mm x 45mm x 7mm. Cross-supplier accessory markup applied (T-Moulding/Reducer +$10, Stair Nose +$15) -&gt; Retail $28.00/pc. Supplier: 'Due to the fragile nature of this product, all sales are final. No Returns or Exchanges.' Sheet groups 'T Moulding / Reducer' at $18.00 and 'Stair Nose Overlap' at $22.00. COST BASIS UNCONFIRMED: the Aug 31 2026 Product Guide prints a single price with no statement of whether it is Titan's dealer cost or suggested retail. Printed price entered in Cost/unit as-is with no multiplier; Retail = Cost + $1.00. May need a dealer multiplier (cf. CIF x0.60, Olympia x0.564, Biyork MSRP-vs-Your-Price) before import - Albert to settle. NEW SUPPLIER - Canadian Standard has no subsection in bert-airtable-schema and no records/Supplier option in Airtable. Global rules only; supplier onboarding checklist still owed. SKU suffix 'CANS' and the LS handle scheme are unconfirmed (CANS implied by the skill's HWD-CANS-0001 format example). | MatchStatus: new</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t>ACCESSORIES</t>
-        </is>
-      </c>
-      <c r="Q338" t="n">
-        <v>18</v>
-      </c>
-      <c r="R338" t="n">
-        <v>28</v>
-      </c>
-      <c r="W338" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="X338" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>Default Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>CANSVANNTETTPROSTAIRNOSING</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>ACC-CANS-0012</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>Canadian Standard - Transition | Stair Nosing | SPC | 2400mm x 53mm x 18mm (VANNTETTPRO)</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>Sold per piece | Last price update: 2026-08-31 | Price last changed by: Manual | Active: TRUE | Salesperson notes: Per-piece trim, 2400mm x 53mm x 18mm. Cross-supplier accessory markup applied (T-Moulding/Reducer +$10, Stair Nose +$15) -&gt; Retail $37.00/pc. Supplier: 'Due to the fragile nature of this product, all sales are final. No Returns or Exchanges.' Sheet groups 'T Moulding / Reducer' at $18.00 and 'Stair Nose Overlap' at $22.00. COST BASIS UNCONFIRMED: the Aug 31 2026 Product Guide prints a single price with no statement of whether it is Titan's dealer cost or suggested retail. Printed price entered in Cost/unit as-is with no multiplier; Retail = Cost + $1.00. May need a dealer multiplier (cf. CIF x0.60, Olympia x0.564, Biyork MSRP-vs-Your-Price) before import - Albert to settle. NEW SUPPLIER - Canadian Standard has no subsection in bert-airtable-schema and no records/Supplier option in Airtable. Global rules only; supplier onboarding checklist still owed. SKU suffix 'CANS' and the LS handle scheme are unconfirmed (CANS implied by the skill's HWD-CANS-0001 format example). | MatchStatus: new</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>ACCESSORIES</t>
-        </is>
-      </c>
-      <c r="Q339" t="n">
-        <v>22</v>
-      </c>
-      <c r="R339" t="n">
-        <v>37</v>
-      </c>
-      <c r="W339" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="X339" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="Z339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB339" t="inlineStr">
-        <is>
-          <t>Default Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>CANSVANNTETTPROTMOULDING</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>ACC-CANS-0010</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>Canadian Standard - Transition | T-Moulding | SPC | 2400mm x 45mm x 7mm (VANNTETTPRO)</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>Sold per piece | Last price update: 2026-08-31 | Price last changed by: Manual | Active: TRUE | Salesperson notes: Per-piece trim, 2400mm x 45mm x 7mm. Cross-supplier accessory markup applied (T-Moulding/Reducer +$10, Stair Nose +$15) -&gt; Retail $28.00/pc. Supplier: 'Due to the fragile nature of this product, all sales are final. No Returns or Exchanges.' Sheet groups 'T Moulding / Reducer' at $18.00 and 'Stair Nose Overlap' at $22.00. COST BASIS UNCONFIRMED: the Aug 31 2026 Product Guide prints a single price with no statement of whether it is Titan's dealer cost or suggested retail. Printed price entered in Cost/unit as-is with no multiplier; Retail = Cost + $1.00. May need a dealer multiplier (cf. CIF x0.60, Olympia x0.564, Biyork MSRP-vs-Your-Price) before import - Albert to settle. NEW SUPPLIER - Canadian Standard has no subsection in bert-airtable-schema and no records/Supplier option in Airtable. Global rules only; supplier onboarding checklist still owed. SKU suffix 'CANS' and the LS handle scheme are unconfirmed (CANS implied by the skill's HWD-CANS-0001 format example). | MatchStatus: new</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>ACCESSORIES</t>
-        </is>
-      </c>
-      <c r="Q340" t="n">
-        <v>18</v>
-      </c>
-      <c r="R340" t="n">
-        <v>28</v>
-      </c>
-      <c r="W340" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="X340" t="inlineStr">
-        <is>
-          <t>Canadian Standard</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA340" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB340" t="inlineStr">
         <is>
           <t>Default Tax</t>
         </is>
